--- a/data/trans_camb/P43E-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P43E-Clase-trans_camb.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9,05</t>
+          <t>9,03</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,05</t>
+          <t>9,03</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,39; -0,38</t>
+          <t>-16,71; 1,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 17,9</t>
+          <t>0,12; 16,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,39; -0,38</t>
+          <t>-16,71; 1,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 17,9</t>
+          <t>0,12; 16,91</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,34%</t>
         </is>
       </c>
     </row>
@@ -657,22 +657,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-40,1; -0,4</t>
+          <t>-38,4; 4,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,56; 53,97</t>
+          <t>0,47; 50,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-40,1; -0,4</t>
+          <t>-38,4; 4,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,56; 53,97</t>
+          <t>0,47; 50,27</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,23</t>
+          <t>2,22</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,23</t>
+          <t>2,22</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,59; 0,64</t>
+          <t>-16,83; 0,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 10,11</t>
+          <t>-5,99; 10,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,59; 0,64</t>
+          <t>-16,83; 0,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 10,11</t>
+          <t>-5,99; 10,34</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -773,22 +773,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-37,56; 2,65</t>
+          <t>-40,35; -0,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,61; 30,5</t>
+          <t>-14,68; 31,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-37,56; 2,65</t>
+          <t>-40,35; -0,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,61; 30,5</t>
+          <t>-14,68; 31,76</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,83</t>
+          <t>2,35</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,83</t>
+          <t>2,35</t>
         </is>
       </c>
     </row>
@@ -833,22 +833,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-23,09; -4,3</t>
+          <t>-23,46; -4,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 13,98</t>
+          <t>-8,84; 15,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-23,09; -4,3</t>
+          <t>-23,46; -4,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 13,98</t>
+          <t>-8,84; 15,45</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -889,22 +889,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-71,31; -17,79</t>
+          <t>-72,24; -14,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-28,54; 59,92</t>
+          <t>-27,15; 67,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-71,31; -17,79</t>
+          <t>-72,24; -14,5</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-28,54; 59,92</t>
+          <t>-27,15; 67,18</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-2,47</t>
+          <t>-2,62</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-2,47</t>
+          <t>-2,62</t>
         </is>
       </c>
     </row>
@@ -949,22 +949,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,09; -0,13</t>
+          <t>-10,1; -0,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 2,46</t>
+          <t>-7,36; 2,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,09; -0,13</t>
+          <t>-10,1; -0,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 2,46</t>
+          <t>-7,36; 2,9</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-12,11%</t>
+          <t>-12,83%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-12,11%</t>
+          <t>-12,83%</t>
         </is>
       </c>
     </row>
@@ -1005,22 +1005,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-42,75; -0,99</t>
+          <t>-43,08; -2,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-33,79; 13,64</t>
+          <t>-32,81; 17,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-42,75; -0,99</t>
+          <t>-43,08; -2,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-33,79; 13,64</t>
+          <t>-32,81; 17,23</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-7,94</t>
+          <t>-5,47</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-7,94</t>
+          <t>-5,47</t>
         </is>
       </c>
     </row>
@@ -1065,22 +1065,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-13,51; -4,9</t>
+          <t>-13,65; -5,28</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-13,08; -3,46</t>
+          <t>-9,81; -1,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,51; -4,9</t>
+          <t>-13,65; -5,28</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-13,08; -3,46</t>
+          <t>-9,81; -1,12</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-52,85%</t>
+          <t>-36,41%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-52,85%</t>
+          <t>-36,41%</t>
         </is>
       </c>
     </row>
@@ -1121,29 +1121,29 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-76,35; -36,02</t>
+          <t>-77,13; -41,17</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-74,54; -26,64</t>
+          <t>-56,0; -7,89</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-76,35; -36,02</t>
+          <t>-77,13; -41,17</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-74,54; -26,64</t>
+          <t>-56,0; -7,89</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-3,33</t>
+          <t>-3,28</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-3,33</t>
+          <t>-3,28</t>
         </is>
       </c>
     </row>
@@ -1181,22 +1181,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-9,01; -0,3</t>
+          <t>-9,01; -0,13</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 1,31</t>
+          <t>-8,06; 1,9</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-9,01; -0,3</t>
+          <t>-9,01; -0,13</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 1,31</t>
+          <t>-8,06; 1,9</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-19,95%</t>
+          <t>-19,68%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-19,95%</t>
+          <t>-19,68%</t>
         </is>
       </c>
     </row>
@@ -1237,22 +1237,22 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-48,29; -1,94</t>
+          <t>-47,36; -0,85</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-43,19; 9,07</t>
+          <t>-41,91; 14,14</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-48,29; -1,94</t>
+          <t>-47,36; -0,85</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-43,19; 9,07</t>
+          <t>-41,91; 14,14</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-0,71</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-0,71</t>
+          <t>0,86</t>
         </is>
       </c>
     </row>
@@ -1297,22 +1297,22 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-9,13; -4,12</t>
+          <t>-8,94; -3,96</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 2,33</t>
+          <t>-1,49; 3,7</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-9,13; -4,12</t>
+          <t>-8,94; -3,96</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 2,33</t>
+          <t>-1,49; 3,7</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-3,09%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-3,09%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -1353,22 +1353,22 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-37,19; -18,62</t>
+          <t>-36,84; -17,73</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-17,44; 10,65</t>
+          <t>-6,08; 17,04</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-37,19; -18,62</t>
+          <t>-36,84; -17,73</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-17,44; 10,65</t>
+          <t>-6,08; 17,04</t>
         </is>
       </c>
     </row>
